--- a/cypress/downloads/Lector Live.xlsx
+++ b/cypress/downloads/Lector Live.xlsx
@@ -201,9 +201,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <cols>
-    <col min="1" max="1" width="8.100000000000001" customWidth="1"/>
-    <col min="2" max="2" width="6.75" customWidth="1"/>
-    <col min="3" max="3" width="8.100000000000001" customWidth="1"/>
+    <col min="1" max="1" width="14.850000000000001" customWidth="1"/>
+    <col min="2" max="2" width="9.450000000000001" customWidth="1"/>
+    <col min="3" max="3" width="14.850000000000001" customWidth="1"/>
     <col min="4" max="4" width="13.5" customWidth="1"/>
     <col min="5" max="5" width="13.5" customWidth="1"/>
     <col min="6" max="6" width="25.650000000000002" customWidth="1"/>
@@ -302,6 +302,41 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c t="inlineStr" r="A4">
+        <is>
+          <t xml:space="preserve">CupomTeste2</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B4">
+        <is>
+          <t xml:space="preserve">R$ 2.00</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C4">
+        <is>
+          <t xml:space="preserve">CupomTeste2</t>
+        </is>
+      </c>
+      <c t="n" r="E4">
+        <v>0</v>
+      </c>
+      <c t="inlineStr" r="F4">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="G4">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H4">
+        <is>
+          <t xml:space="preserve">R$ 5.00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
